--- a/Team-Data/2007-08/3-25-2007-08.xlsx
+++ b/Team-Data/2007-08/3-25-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
         <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>0.429</v>
+        <v>0.435</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,7 +746,7 @@
         <v>35.7</v>
       </c>
       <c r="J2" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.448</v>
@@ -694,13 +761,13 @@
         <v>0.352</v>
       </c>
       <c r="O2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>27.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R2" t="n">
         <v>12.4</v>
@@ -712,7 +779,7 @@
         <v>42.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.2</v>
@@ -721,31 +788,31 @@
         <v>7.4</v>
       </c>
       <c r="X2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y2" t="n">
         <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB2" t="n">
         <v>96.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
         <v>19</v>
@@ -790,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV2" t="n">
         <v>25</v>
@@ -802,10 +869,10 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>9.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -963,7 +1030,7 @@
         <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
         <v>9</v>
@@ -984,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -993,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>0.357</v>
+        <v>0.362</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,25 +1110,25 @@
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M4" t="n">
         <v>17.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P4" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.71</v>
@@ -1070,16 +1137,16 @@
         <v>11.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U4" t="n">
         <v>20.9</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.5</v>
@@ -1091,19 +1158,19 @@
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.2</v>
+        <v>-4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1118,10 +1185,10 @@
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>23</v>
@@ -1148,16 +1215,16 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
         <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K5" t="n">
         <v>0.43</v>
@@ -1234,22 +1301,22 @@
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R5" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="S5" t="n">
         <v>30.3</v>
@@ -1261,37 +1328,37 @@
         <v>21.7</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
         <v>21.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
         <v>96.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1300,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,7 +1385,7 @@
         <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
@@ -1345,7 +1412,7 @@
         <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.634</v>
+        <v>0.629</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1592,7 +1659,7 @@
         <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
@@ -1601,10 +1668,10 @@
         <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O7" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P7" t="n">
         <v>25.5</v>
@@ -1613,28 +1680,28 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S7" t="n">
         <v>32.5</v>
       </c>
       <c r="T7" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
         <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
         <v>21.9</v>
@@ -1646,10 +1713,10 @@
         <v>100</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1658,10 +1725,10 @@
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1670,7 +1737,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="n">
         <v>19</v>
@@ -1691,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
         <v>4</v>
@@ -1709,10 +1776,10 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>22</v>
@@ -1724,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1846,7 +1913,7 @@
         <v>13</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
         <v>3</v>
@@ -1873,7 +1940,7 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2043,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
         <v>14</v>
@@ -2079,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2389,7 +2456,7 @@
         <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI11" t="n">
         <v>15</v>
@@ -2428,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" t="n">
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.408</v>
+        <v>0.414</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L12" t="n">
         <v>9</v>
@@ -2514,13 +2581,13 @@
         <v>0.369</v>
       </c>
       <c r="O12" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
@@ -2532,7 +2599,7 @@
         <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V12" t="n">
         <v>15.2</v>
@@ -2550,22 +2617,22 @@
         <v>23.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>21</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3</v>
+        <v>0.304</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2690,16 +2757,16 @@
         <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.324</v>
+        <v>0.327</v>
       </c>
       <c r="O13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P13" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0.783</v>
@@ -2711,10 +2778,10 @@
         <v>30.3</v>
       </c>
       <c r="T13" t="n">
-        <v>39.8</v>
+        <v>39.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V13" t="n">
         <v>14.3</v>
@@ -2735,13 +2802,13 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2792,7 +2859,7 @@
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2804,7 +2871,7 @@
         <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3162,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>28</v>
@@ -3341,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-6.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
@@ -3529,7 +3596,7 @@
         <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3696,7 +3763,7 @@
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3863,7 +3930,7 @@
         <v>19</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3875,13 +3942,13 @@
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3896,7 +3963,7 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3958,34 +4025,34 @@
         <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N20" t="n">
         <v>0.39</v>
       </c>
       <c r="O20" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P20" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="Q20" t="n">
         <v>0.771</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>30.7</v>
       </c>
       <c r="T20" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
@@ -4009,16 +4076,16 @@
         <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>3</v>
@@ -4036,10 +4103,10 @@
         <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
         <v>9</v>
@@ -4063,16 +4130,16 @@
         <v>14</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4242,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>0.63</v>
+        <v>0.639</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4325,10 +4392,10 @@
         <v>0.473</v>
       </c>
       <c r="L22" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="N22" t="n">
         <v>0.386</v>
@@ -4340,55 +4407,55 @@
         <v>28.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R22" t="n">
         <v>9.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
         <v>42.1</v>
       </c>
       <c r="U22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V22" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X22" t="n">
         <v>4.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.5</v>
+        <v>104.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF22" t="n">
         <v>9</v>
       </c>
-      <c r="AF22" t="n">
-        <v>10</v>
-      </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
@@ -4433,28 +4500,28 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
         <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB22" t="n">
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
@@ -4573,7 +4640,7 @@
         <v>16</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH24" t="n">
         <v>16</v>
@@ -4797,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.528</v>
+        <v>0.521</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J25" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L25" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
         <v>17.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O25" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P25" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="n">
         <v>0.768</v>
       </c>
       <c r="R25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T25" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
         <v>13</v>
@@ -4919,10 +4986,10 @@
         <v>20.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
         <v>2</v>
@@ -4931,10 +4998,10 @@
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
@@ -4955,10 +5022,10 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -4967,16 +5034,16 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV25" t="n">
         <v>5</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -4997,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,13 +5186,13 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
         <v>11</v>
@@ -5140,7 +5207,7 @@
         <v>9</v>
       </c>
       <c r="AO26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP26" t="n">
         <v>6</v>
@@ -5155,7 +5222,7 @@
         <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.676</v>
+        <v>0.671</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
@@ -5232,7 +5299,7 @@
         <v>78.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L27" t="n">
         <v>7.5</v>
@@ -5244,22 +5311,22 @@
         <v>0.372</v>
       </c>
       <c r="O27" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P27" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q27" t="n">
         <v>0.765</v>
       </c>
       <c r="R27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S27" t="n">
         <v>31.4</v>
       </c>
       <c r="T27" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U27" t="n">
         <v>21.2</v>
@@ -5268,43 +5335,43 @@
         <v>12.7</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X27" t="n">
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z27" t="n">
         <v>19</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="n">
         <v>5</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI27" t="n">
         <v>26</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>25</v>
       </c>
       <c r="AJ27" t="n">
         <v>25</v>
@@ -5331,7 +5398,7 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>10</v>
@@ -5340,7 +5407,7 @@
         <v>20</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5361,7 +5428,7 @@
         <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5531,7 +5598,7 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>17</v>
@@ -5665,7 +5732,7 @@
         <v>17</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5824,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F30" t="n">
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.653</v>
+        <v>0.648</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J30" t="n">
         <v>80.40000000000001</v>
@@ -5784,28 +5851,28 @@
         <v>4.7</v>
       </c>
       <c r="M30" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R30" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S30" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T30" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U30" t="n">
         <v>26.3</v>
@@ -5814,10 +5881,10 @@
         <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
         <v>5.3</v>
@@ -5826,19 +5893,19 @@
         <v>24.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.5</v>
+        <v>106.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5850,7 +5917,7 @@
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ30" t="n">
         <v>18</v>
@@ -5868,7 +5935,7 @@
         <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>2</v>
@@ -5877,19 +5944,19 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" t="n">
         <v>36</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.514</v>
+        <v>0.522</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
         <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L31" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O31" t="n">
         <v>19.1</v>
@@ -5984,16 +6051,16 @@
         <v>12.2</v>
       </c>
       <c r="S31" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T31" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U31" t="n">
         <v>19.2</v>
       </c>
       <c r="V31" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W31" t="n">
         <v>7.8</v>
@@ -6002,7 +6069,7 @@
         <v>4.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
         <v>19.7</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6026,13 +6093,13 @@
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>13</v>
@@ -6047,13 +6114,13 @@
         <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>4</v>
@@ -6062,7 +6129,7 @@
         <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6080,7 +6147,7 @@
         <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-25-2007-08</t>
+          <t>2008-03-25</t>
         </is>
       </c>
     </row>
